--- a/entregables/SIGRO - Product Backlog v6.xlsx
+++ b/entregables/SIGRO - Product Backlog v6.xlsx
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="I40" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -6076,13 +6076,13 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>29 historias · 152 puntos · capacidad estimada del equipo: 4 personas × 8-12 h/semana × 2 semanas ≈ 80 h. Referencia: 1 punto ≈ 2 h.</t>
+          <t>29 historias · 153 puntos · capacidad estimada del equipo: 4 personas × 8-12 h/semana × 2 semanas ≈ 80 h. Referencia: 1 punto ≈ 2 h.</t>
         </is>
       </c>
     </row>

--- a/entregables/SIGRO - Product Backlog v6.xlsx
+++ b/entregables/SIGRO - Product Backlog v6.xlsx
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v6 · 15/10/2026 · incorpora los acuerdos de la reunión con el cliente y la revisión del Ing. Junior Cercado</t>
+          <t>v6 · 15/10/2026 · incorpora los acuerdos de la reunión con el cliente y la revisión técnica del cliente</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Reunión con SEVENS INGENIEROS SAC (oct. 2026) · revisión del Ing. Junior Cercado (15/10/2026)</t>
+          <t>Reunión con SEVENS INGENIEROS SAC (oct. 2026) · revisión técnica del cliente (15/10/2026)</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Tanto el cliente como el Ing. Junior Cercado coinciden en que exigen cruzar partidas y metrados, con alto esfuerzo y poco retorno para este alcance.</t>
+          <t>El cliente coincide en que exigen cruzar partidas y metrados, con alto esfuerzo y poco retorno para este alcance.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>El Ing. Junior Cercado recomendó mover a Post-MVP lo de bajo valor frente al problema central.</t>
+          <t>El cliente recomendó mover a Post-MVP lo de bajo valor frente al problema central.</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
